--- a/AAII_Financials/Quarterly/PM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>PM</t>
   </si>
@@ -656,526 +656,539 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="42" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="43" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
-      </c>
-      <c r="R7" s="2">
-        <v>44834</v>
       </c>
       <c r="S7" s="2">
         <v>44834</v>
       </c>
       <c r="T7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11192000</v>
+      </c>
+      <c r="E8" s="3">
         <v>10146000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10362000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10845000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10140000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9301000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9706000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9911000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9468000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8793000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9047000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9141000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8967000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8019000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8152000</v>
-      </c>
-      <c r="R8" s="3">
-        <v>8032000</v>
       </c>
       <c r="S8" s="3">
         <v>8032000</v>
       </c>
       <c r="T8" s="3">
+        <v>8032000</v>
+      </c>
+      <c r="U8" s="3">
         <v>7746000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8104000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8122000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7594000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7585000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7444000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7446000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6651000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7153000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7713000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7642000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7699000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6751000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7499000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7504000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7726000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6896000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>8294000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7473000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6917000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6064000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>6971000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>6982000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3533000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3241000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3560000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3487000</v>
       </c>
-      <c r="G9" s="3">
-        <v>3279000</v>
-      </c>
       <c r="H9" s="3">
+        <v>3274000</v>
+      </c>
+      <c r="I9" s="3">
         <v>3031000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3423000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3366000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3345000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3195000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3426000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3165000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3228000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3020000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3195000</v>
-      </c>
-      <c r="R9" s="3">
-        <v>2823000</v>
       </c>
       <c r="S9" s="3">
         <v>2823000</v>
       </c>
       <c r="T9" s="3">
+        <v>2823000</v>
+      </c>
+      <c r="U9" s="3">
         <v>2582000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2807000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2596000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2353000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2274000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2572000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2416000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2179000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2402000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2778000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2605000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2665000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2465000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2781000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2618000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2744000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2615000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3001000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2735000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2519000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2177000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2499000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2432000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7659000</v>
+      </c>
+      <c r="E10" s="3">
         <v>6905000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6802000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7358000</v>
       </c>
-      <c r="G10" s="3">
-        <v>6861000</v>
-      </c>
       <c r="H10" s="3">
+        <v>6866000</v>
+      </c>
+      <c r="I10" s="3">
         <v>6270000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6283000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6545000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6123000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5598000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5621000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5976000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5739000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4999000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4957000</v>
-      </c>
-      <c r="R10" s="3">
-        <v>5209000</v>
       </c>
       <c r="S10" s="3">
         <v>5209000</v>
       </c>
       <c r="T10" s="3">
+        <v>5209000</v>
+      </c>
+      <c r="U10" s="3">
         <v>5164000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5297000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5526000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5241000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5311000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4872000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5030000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4472000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4751000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4935000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5037000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5034000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4286000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4718000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4886000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4982000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4281000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5293000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4738000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4398000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3887000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>4472000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>4550000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1218,19 +1231,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>756000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1238,11 +1252,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>759000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1250,11 +1264,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>694000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1340,8 +1354,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1462,100 +1479,103 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>517000</v>
+      </c>
+      <c r="E14" s="3">
         <v>24000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-118000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>157000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>284000</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2329000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>243000</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>195000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>55000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>159000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>680000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>127000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>138000</v>
-      </c>
-      <c r="R14" s="3">
-        <v>118000</v>
       </c>
       <c r="S14" s="3">
         <v>118000</v>
       </c>
       <c r="T14" s="3">
+        <v>118000</v>
+      </c>
+      <c r="U14" s="3">
         <v>42000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>46000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>43000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>79000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>48000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>78000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>71000</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>357000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>22000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>23000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>453000</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
@@ -1566,11 +1586,11 @@
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
       </c>
       <c r="AM14" s="3" t="s">
         <v>8</v>
@@ -1578,58 +1598,61 @@
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>513000</v>
+      </c>
+      <c r="E15" s="3">
         <v>510000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>521000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>505000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>490000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>480000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>477000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>498000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>445000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>367000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>369000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>429000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>60000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>299000</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>8</v>
@@ -1637,20 +1660,20 @@
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U15" s="3">
         <v>38000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>41000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>18000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>19000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>18000</v>
       </c>
       <c r="Y15" s="3">
         <v>18000</v>
@@ -1659,55 +1682,58 @@
         <v>18000</v>
       </c>
       <c r="AA15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AB15" s="3">
         <v>19000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>18000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>16000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>15000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>16000</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>19000</v>
       </c>
       <c r="AG15" s="3">
         <v>19000</v>
       </c>
       <c r="AH15" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AI15" s="3">
         <v>20000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>22000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>23000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>21000</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>22000</v>
       </c>
       <c r="AN15" s="3">
         <v>22000</v>
       </c>
       <c r="AO15" s="3">
+        <v>22000</v>
+      </c>
+      <c r="AP15" s="3">
         <v>18000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1747,252 +1773,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6715000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6489000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6949000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6426000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5061000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5486000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7011000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5607000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5941000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6104000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5358000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5859000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5694000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5167000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5228000</v>
-      </c>
-      <c r="R17" s="3">
-        <v>5064000</v>
       </c>
       <c r="S17" s="3">
         <v>5064000</v>
       </c>
       <c r="T17" s="3">
+        <v>5064000</v>
+      </c>
+      <c r="U17" s="3">
         <v>4448000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5157000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4667000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4465000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4141000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4539000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4203000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3920000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4364000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5207000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4854000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4512000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4701000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4797000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4348000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4633000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4470000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4954000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4385000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4180000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3668000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>4359000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>4005000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4477000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3657000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3413000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4419000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5079000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3815000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2695000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4304000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3527000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2689000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3689000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3282000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3273000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2852000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2924000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>2968000</v>
       </c>
       <c r="S18" s="3">
         <v>2968000</v>
       </c>
       <c r="T18" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="U18" s="3">
         <v>3298000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2947000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3455000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3129000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3444000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2905000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3243000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2731000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2789000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2506000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2788000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3187000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2050000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2702000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3156000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3093000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2426000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3340000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3088000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2737000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2396000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2612000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2977000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2035,297 +2068,304 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-378000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-16000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>884000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-505000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>558000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-85000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>82000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-265000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-192000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-840000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1127000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-466000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-69000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-188000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-178000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-145000</v>
       </c>
       <c r="S20" s="3">
         <v>-145000</v>
       </c>
       <c r="T20" s="3">
+        <v>-145000</v>
+      </c>
+      <c r="U20" s="3">
         <v>-158000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-179000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-181000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-188000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-195000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-193000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-186000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-184000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-152000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-164000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-152000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-170000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-173000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-147000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-152000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-174000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-233000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-281000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-243000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-229000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-219000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-201000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-220000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5368000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4183000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3050000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5429000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5011000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4380000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3090000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5067000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4164000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3896000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2931000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4177000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3402000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3339000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3037000</v>
-      </c>
-      <c r="R21" s="3">
-        <v>3181000</v>
       </c>
       <c r="S21" s="3">
         <v>3181000</v>
       </c>
       <c r="T21" s="3">
+        <v>3181000</v>
+      </c>
+      <c r="U21" s="3">
         <v>3393000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3047000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3509000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3180000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3494000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2984000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3296000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2776000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2878000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2597000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2873000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3249000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2117000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2810000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3250000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3165000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2435000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3302000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3070000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2718000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2374000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2606000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>2945000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>398000</v>
+      </c>
+      <c r="E22" s="3">
         <v>391000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>343000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>403000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>437000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>404000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>518000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>376000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>457000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>412000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>339000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>387000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>420000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>383000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2401,252 +2441,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3940000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3258000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2925000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4364000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3800000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3496000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>386000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3950000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3262000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2922000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2633000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3202000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2242000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2530000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2746000</v>
-      </c>
-      <c r="R23" s="3">
-        <v>2823000</v>
       </c>
       <c r="S23" s="3">
         <v>2823000</v>
       </c>
       <c r="T23" s="3">
+        <v>2823000</v>
+      </c>
+      <c r="U23" s="3">
         <v>3140000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2768000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3274000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2941000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3249000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2712000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3057000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2547000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2637000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2342000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2636000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3017000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1877000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2555000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3004000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2919000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2193000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3059000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2845000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2508000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2177000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2411000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2757000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>955000</v>
+      </c>
+      <c r="E24" s="3">
         <v>676000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>675000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>751000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>652000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>659000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>872000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>735000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>734000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>676000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>320000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1031000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>560000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>428000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>409000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>622000</v>
       </c>
       <c r="S24" s="3">
         <v>622000</v>
       </c>
       <c r="T24" s="3">
+        <v>622000</v>
+      </c>
+      <c r="U24" s="3">
         <v>619000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>593000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>735000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>646000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>697000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>613000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>640000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>528000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>596000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>623000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>635000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>611000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>424000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>520000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>691000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>644000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>559000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>665000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>812000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>689000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>541000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>658000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>764000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2767,252 +2816,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2985000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2582000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2250000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3613000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3148000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2837000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-486000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3215000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2528000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2246000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2313000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2171000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1682000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2102000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2337000</v>
-      </c>
-      <c r="R26" s="3">
-        <v>2201000</v>
       </c>
       <c r="S26" s="3">
         <v>2201000</v>
       </c>
       <c r="T26" s="3">
+        <v>2201000</v>
+      </c>
+      <c r="U26" s="3">
         <v>2521000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2175000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2539000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2295000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2552000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2099000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2417000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2019000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2041000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1719000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2001000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2406000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1453000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2035000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2313000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2275000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1634000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2394000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2033000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1819000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1636000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1753000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1993000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2810000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2431000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2135000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3468000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3031000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2682000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-580000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3073000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2399000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2142000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2191000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2048000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1563000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1989000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2391000</v>
-      </c>
-      <c r="R27" s="3">
-        <v>2082000</v>
       </c>
       <c r="S27" s="3">
         <v>2082000</v>
       </c>
       <c r="T27" s="3">
+        <v>2082000</v>
+      </c>
+      <c r="U27" s="3">
         <v>2324000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2088000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2419000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2166000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2411000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1971000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2302000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1942000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1821000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1612000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1891000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2314000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1350000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1938000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2242000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2193000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1553000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2292000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1966000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1776000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1587000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1707000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3133,8 +3191,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3207,8 +3268,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3225,11 +3286,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-31000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3237,11 +3298,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-1600000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3255,8 +3316,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3377,8 +3441,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3499,252 +3566,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>378000</v>
+      </c>
+      <c r="E32" s="3">
         <v>16000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-884000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>505000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-558000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>85000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-82000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>265000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>192000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>840000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1127000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>466000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>69000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>188000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>178000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>145000</v>
       </c>
       <c r="S32" s="3">
         <v>145000</v>
       </c>
       <c r="T32" s="3">
+        <v>145000</v>
+      </c>
+      <c r="U32" s="3">
         <v>158000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>179000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>181000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>188000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>195000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>193000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>186000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>184000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>152000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>164000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>152000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>170000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>173000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>147000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>152000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>174000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>233000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>281000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>243000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>229000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>219000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>201000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>220000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2817000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2438000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2141000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3478000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3039000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2690000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-579000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3082000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2406000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2148000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2196000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2054000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1568000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1995000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2391000</v>
-      </c>
-      <c r="R33" s="3">
-        <v>2082000</v>
       </c>
       <c r="S33" s="3">
         <v>2082000</v>
       </c>
       <c r="T33" s="3">
+        <v>2082000</v>
+      </c>
+      <c r="U33" s="3">
         <v>2324000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2088000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2419000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2166000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2411000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1971000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2302000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1942000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1821000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1612000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1891000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2314000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1350000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1907000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2242000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2193000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1553000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>692000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1966000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1776000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1587000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1707000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3865,257 +3941,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2817000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2438000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2141000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3478000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3039000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2690000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-579000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3082000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2406000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2148000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2196000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2054000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1568000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1995000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2391000</v>
-      </c>
-      <c r="R35" s="3">
-        <v>2082000</v>
       </c>
       <c r="S35" s="3">
         <v>2082000</v>
       </c>
       <c r="T35" s="3">
+        <v>2082000</v>
+      </c>
+      <c r="U35" s="3">
         <v>2324000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2088000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2419000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2166000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2411000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1971000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2302000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1942000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1821000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1612000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1891000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2314000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1350000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1907000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2242000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2193000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1553000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>692000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1966000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1776000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1587000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1707000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
-      </c>
-      <c r="R38" s="2">
-        <v>44834</v>
       </c>
       <c r="S38" s="2">
         <v>44834</v>
       </c>
       <c r="T38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4158,8 +4243,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4202,148 +4288,152 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5999000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5450000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4872000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4037000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4138000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4443000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4216000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4258000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4807000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3968000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3060000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3017000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3492000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2428000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3207000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5368000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5036000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4622000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4496000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4491000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4915000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3902000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7280000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4821000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4200000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3746000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6861000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6507000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4008000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3081000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6593000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5880000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6587000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>7200000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8447000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>7667000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6197000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5076000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>4239000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>4884000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E42" s="3">
         <v>13000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>7000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -4357,11 +4447,11 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>1000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -4446,862 +4536,886 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6474000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6390000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5810000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5823000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5889000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5793000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4675000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5191000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5117000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5052000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4391000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4789000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5012000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4599000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4756000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4611000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4593000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4418000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3940000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4182000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4445000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4087000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3761000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3712000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3944000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3334000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3717000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3729000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4074000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3535000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3564000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3522000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3772000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3894000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3738000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3985000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3648000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3090000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3499000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3100000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>11436000</v>
+      </c>
+      <c r="E44" s="3">
         <v>11392000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11478000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10267000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10728000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10127000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9453000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9355000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9382000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9970000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10774000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9645000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9900000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10712000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>9886000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7153000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7551000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8684000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8720000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8173000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>8690000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>9019000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>9591000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>8160000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>8968000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>9045000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>9235000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>8529000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>8255000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>8318000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>8804000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>8440000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>8925000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>8592000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>8806000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>8283000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>7730000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>8007000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>9017000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>7486000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2068000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2337000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2183000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2507000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2568000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1800000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1788000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1949000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1653000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1753000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1443000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1725000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1412000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1814000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1770000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1903000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1196000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1000000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>561000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1000000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>693000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>902000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>860000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>760000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>664000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>736000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>701000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>810000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>826000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>807000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>481000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>696000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>744000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>907000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>603000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>924000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>857000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>711000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>853000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1104000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26006000</v>
+      </c>
+      <c r="E46" s="3">
         <v>25602000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24363000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22665000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23364000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22196000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20170000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20796000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21028000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20874000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19755000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>19193000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>19836000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>19571000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>19619000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>19035000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18376000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18724000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17717000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17846000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18743000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17910000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>21492000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17453000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17776000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16861000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>20514000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>19575000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17163000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15741000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>19442000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>18538000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>20028000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>20593000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>21594000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>20859000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>18432000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>16884000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>17608000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>16574000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2142000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2518000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2968000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3210000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3418000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3024000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2658000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5631000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4961000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4918000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4929000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4691000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4747000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4504000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4431000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4087000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4328000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4312000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4463000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4624000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4633000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4637000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4798000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4579000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4516000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4390000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4635000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4499000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4665000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4578000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1269000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1361000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1352000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1395000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1074000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1080000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1072000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1079000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1011000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>986000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8313000</v>
+      </c>
+      <c r="E48" s="3">
         <v>8259000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9076000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8115000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8043000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7532000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7895000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7548000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7264000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7201000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8147000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6883000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6991000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6788000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6710000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5610000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5965000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6004000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6694000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6061000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5975000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5952000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7062000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6134000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6184000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6107000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7397000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7352000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7627000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7601000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7201000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7138000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7113000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7459000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>21837000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>6857000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>6629000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>6264000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>6064000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>6133000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27095000</v>
+      </c>
+      <c r="E49" s="3">
         <v>27581000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>28148000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>28327000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>28607000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>28209000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>27927000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>29060000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>28990000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>25906000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>26643000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>26088000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>25866000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>26598000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>26387000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8351000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8974000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9418000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9498000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9707000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7800000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7720000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7983000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7573000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7601000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7134000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7971000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7808000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7958000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7904000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>9467000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>9588000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9648000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>10122000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>10732000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>10182000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>10141000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>10002000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>9794000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>10224000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5422,8 +5536,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5544,130 +5661,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3578000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3756000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3383000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3687000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3963000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2831000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2194000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2845000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2621000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5466000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5016000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5495000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3854000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4014000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4534000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3634000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3317000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3275000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2918000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3351000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3535000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3585000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3480000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3390000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3085000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3002000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2358000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2186000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2510000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2218000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2422000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2755000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2580000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3501000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2931000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2973000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2386000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2398000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>2374000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1660000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5788,130 +5911,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>68271000</v>
+      </c>
+      <c r="E54" s="3">
         <v>68913000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>69185000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>67061000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>68506000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>65079000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>61784000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>66892000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>65782000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>65315000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>65304000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>62927000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>61868000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>62060000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>61681000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40717000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>40960000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>41733000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>41290000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>41589000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>40686000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>39804000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>44815000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>39129000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>39162000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>37494000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>42875000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>41420000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>39923000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>38042000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>39801000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>39380000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>40721000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>43070000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>42968000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>41951000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>38660000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>36627000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>36851000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>35577000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5954,8 +6083,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5998,740 +6128,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3919000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3927000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4407000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3978000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3870000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3749000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3952000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3511000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3591000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3648000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4143000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3533000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3786000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3945000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4076000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3342000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3279000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3203000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3331000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2810000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2630000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2537000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2780000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2155000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1991000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2073000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2299000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1704000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1708000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1812000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2068000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1662000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1953000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2156000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2242000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1973000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1909000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1746000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1666000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1573000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6751000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8163000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3935000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8260000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9062000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10852000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3756000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5028000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4533000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5746000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6941000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4841000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6531000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6739000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8248000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5459000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5707000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5338000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3023000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3337000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1744000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2122000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3368000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2144000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2585000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3371000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4389000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>5390000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>5031000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7133000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4784000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3587000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3617000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>5270000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3005000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>5910000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>5152000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>2758000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>3216000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>3127000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3702000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3780000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4386000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4094000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4173000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3673000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3454000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3793000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3242000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3103000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3958000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3432000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3404000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3445000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15012000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11971000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11561000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11876000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12901000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11730000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11510000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10556000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13467000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11226000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11216000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11140000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12145000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10951000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11307000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9541000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10339000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>10350000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11871000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>10262000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>10715000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>10631000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>10182000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>8851000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>11585000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>9558000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26542000</v>
+      </c>
+      <c r="E60" s="3">
         <v>26222000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25427000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26719000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28148000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28087000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22915000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23366000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22416000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22168000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26383000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21547000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23245000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22985000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27336000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>20772000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>20547000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>20417000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>19255000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17877000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>15884000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>15215000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>19615000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>15525000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>15792000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>16584000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>18833000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>18045000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>18046000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>18486000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>17191000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>15599000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>17441000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>17688000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>15962000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>18514000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>17243000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>13355000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>16467000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>14258000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>42388000</v>
+      </c>
+      <c r="E61" s="3">
         <v>43812000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>45660000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>41863000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>42431000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>38781000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>42596000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44243000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>44663000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>44712000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>41717000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42964000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>41443000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>40462000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>34875000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21762000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>22345000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>24019000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24783000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>25768000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>27414000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>27276000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>28168000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>27346000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>27043000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>24999000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>26656000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>26426000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>24858000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>23131000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>26975000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>28179000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>28048000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>29578000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>31334000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>28065000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>26595000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>28588000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>25851000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>26960000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3941000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4166000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2602000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5464000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5787000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4320000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1512000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4449000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3994000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4334000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2105000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3219000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3430000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3844000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5781000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5586000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5328000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5500000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5460000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6576000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6588000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6887000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7663000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6503000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6447000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6974000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6985000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6104000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6428000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6610000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6374000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5544000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5400000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6286000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5902000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5005000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>5099000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>5241000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>5433000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>4676000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6852,8 +7001,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6974,8 +7126,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7096,130 +7251,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>74928000</v>
+      </c>
+      <c r="E66" s="3">
         <v>76213000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>77213000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>76045000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>78518000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>74005000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>71654000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>74605000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73724000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>73878000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>74750000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>70633000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>69828000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>69113000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>70638000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>49854000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>50004000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51831000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>51396000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>52140000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51799000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>51352000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>57382000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>51221000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>51159000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>50438000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>54452000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>52430000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>51122000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>50010000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>52260000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>51100000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>52636000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>55420000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>55054000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>53358000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>50668000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>49019000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>49539000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>47719000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7262,8 +7423,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7384,8 +7546,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7506,8 +7671,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7628,8 +7796,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7750,130 +7921,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>36055000</v>
+      </c>
+      <c r="E72" s="3">
         <v>35538000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>35400000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>35557000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>34376000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>33447000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>32869000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>35556000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>34582000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>34208000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>34090000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>33919000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>33893000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>34303000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>34289000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>33865000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>33755000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>33468000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>33082000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>32935000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>32465000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>32178000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31638000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31537000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>31103000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>30984000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>30987000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>31197000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>31128000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>30588000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>31014000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>30877000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>30406000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>29985000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>29859000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>30831000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>30528000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>30367000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>30397000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>30305000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7994,8 +8171,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8116,8 +8296,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8238,130 +8421,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-8583000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-9279000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-9994000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-10914000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-11966000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-10901000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-11750000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-9694000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-9744000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-10309000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-11225000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-9433000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-9703000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-8924000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-8957000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-9137000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-9044000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-10098000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-10106000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-10551000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-11113000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-11548000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-12567000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-12092000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-11997000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-12944000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-11577000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-11010000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-11199000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-11968000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-12459000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-11720000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-11915000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-12350000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-12086000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>-11407000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>-12008000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>-12392000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>-12688000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>-12142000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8482,257 +8671,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
-      </c>
-      <c r="R80" s="2">
-        <v>44834</v>
       </c>
       <c r="S80" s="2">
         <v>44834</v>
       </c>
       <c r="T80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2817000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2438000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2141000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3478000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3039000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2690000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-579000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3082000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2406000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2148000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2196000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2054000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1568000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1995000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2391000</v>
-      </c>
-      <c r="R81" s="3">
-        <v>2082000</v>
       </c>
       <c r="S81" s="3">
         <v>2082000</v>
       </c>
       <c r="T81" s="3">
+        <v>2082000</v>
+      </c>
+      <c r="U81" s="3">
         <v>2324000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2088000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2419000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2166000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2411000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1971000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2302000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1942000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1821000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1612000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1891000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2314000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1350000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1907000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2242000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2193000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1553000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>692000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1966000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1776000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1587000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1707000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8775,130 +8973,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>240000</v>
+      </c>
+      <c r="E83" s="3">
         <v>234000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>230000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>242000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>233000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>247000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>240000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>224000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>219000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>218000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>121000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>331000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>251000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>215000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>291000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>358000</v>
       </c>
       <c r="S83" s="3">
         <v>358000</v>
       </c>
       <c r="T83" s="3">
+        <v>358000</v>
+      </c>
+      <c r="U83" s="3">
         <v>253000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>279000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>235000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>239000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>245000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>272000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>239000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>229000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>241000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>255000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>237000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>232000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>240000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>255000</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>246000</v>
       </c>
       <c r="AI83" s="3">
         <v>246000</v>
       </c>
       <c r="AJ83" s="3">
+        <v>246000</v>
+      </c>
+      <c r="AK83" s="3">
         <v>242000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>243000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>225000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>210000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>197000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>195000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>188000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9019,8 +9221,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9141,8 +9346,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9263,8 +9471,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9385,8 +9596,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9507,130 +9721,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5492000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-399000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4709000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4462000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3412000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-350000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4002000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3342000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4632000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>241000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3302000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3415000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3442000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-955000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3093000</v>
-      </c>
-      <c r="R89" s="3">
-        <v>3068000</v>
       </c>
       <c r="S89" s="3">
         <v>3068000</v>
       </c>
       <c r="T89" s="3">
+        <v>3068000</v>
+      </c>
+      <c r="U89" s="3">
         <v>1118000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4032000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3870000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3630000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>435000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3162000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3614000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1925000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1111000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3324000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2083000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3442000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1241000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2422000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1683000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3993000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1380000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2921000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1920000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3228000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>843000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>2149000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>3092000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9673,130 +9893,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-380000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-353000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-444000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-365000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-356000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-404000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-278000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-379000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-370000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-417000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-311000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-371000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-360000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-279000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-347000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-252000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-249000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-229000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-289000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-152000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-128000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-179000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-140000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-152000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-140000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-170000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-156000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-194000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-178000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-324000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-334000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-409000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-365000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-553000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-435000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-268000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-584000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-438000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-254000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9917,8 +10141,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10039,130 +10266,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-428000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-789000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2316000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-434000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>441000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1003000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-337000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-193000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-568000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1956000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-483000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-591000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15528000</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-96000</v>
       </c>
       <c r="S94" s="3">
         <v>-96000</v>
       </c>
       <c r="T94" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="U94" s="3">
         <v>-196000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-340000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1890000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-183000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>55000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-586000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-434000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-648000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>514000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-184000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>122000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-153000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1596000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>166000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-481000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>335000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1018000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-722000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1053000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-696000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-543000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-25000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-506000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10205,115 +10438,116 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2297000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2307000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2295000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2107000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2106000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2116000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2106000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>2027000</v>
       </c>
       <c r="K96" s="3">
         <v>2027000</v>
       </c>
       <c r="L96" s="3">
+        <v>2027000</v>
+      </c>
+      <c r="M96" s="3">
         <v>2037000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2023000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>1977000</v>
       </c>
       <c r="O96" s="3">
         <v>1977000</v>
       </c>
       <c r="P96" s="3">
+        <v>1977000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>1987000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1973000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-1942000</v>
       </c>
       <c r="S96" s="3">
         <v>-1942000</v>
       </c>
       <c r="T96" s="3">
-        <v>-1952000</v>
+        <v>-1942000</v>
       </c>
       <c r="U96" s="3">
         <v>-1952000</v>
       </c>
       <c r="V96" s="3">
+        <v>-1952000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-1876000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1873000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-1879000</v>
       </c>
       <c r="Y96" s="3">
         <v>-1879000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-1879000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1827000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1830000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1828000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1825000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1779000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1777000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1780000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1775000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1778000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1673000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1659000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1666000</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-1618000</v>
       </c>
       <c r="AM96" s="3">
         <v>-1618000</v>
@@ -10322,13 +10556,16 @@
         <v>-1618000</v>
       </c>
       <c r="AO96" s="3">
+        <v>-1618000</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-1619000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-1586000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10449,8 +10686,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10571,8 +10811,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10693,370 +10936,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4975000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1096000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3581000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3661000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1561000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>671000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4103000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2981000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3532000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1135000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2897000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1765000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1784000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>864000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>9877000</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-2271000</v>
       </c>
       <c r="S100" s="3">
         <v>-2271000</v>
       </c>
       <c r="T100" s="3">
+        <v>-2271000</v>
+      </c>
+      <c r="U100" s="3">
         <v>-701000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3801000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2053000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2474000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3649000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-465000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2528000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-954000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4549000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2959000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>453000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2404000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3151000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1747000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1889000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4277000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1738000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1537000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>359000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1932000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>341000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1853000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1566000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E101" s="3">
         <v>335000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-387000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>67000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>14000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-230000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>275000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-172000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-109000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-89000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>401000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-370000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-149000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-95000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>401000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-370000</v>
       </c>
       <c r="S101" s="3">
         <v>-370000</v>
       </c>
       <c r="T101" s="3">
+        <v>-370000</v>
+      </c>
+      <c r="U101" s="3">
         <v>-95000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-191000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-47000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>41000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-220000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>347000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-32000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>134000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-191000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>173000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-160000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>42000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-134000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-660000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>131000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>118000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>247000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>486000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>234000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-916000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>50000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>554000</v>
+      </c>
+      <c r="E102" s="3">
         <v>578000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>831000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-115000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-300000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>222000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-47000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-575000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>777000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>953000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>112000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-478000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1066000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-771000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2157000</v>
-      </c>
-      <c r="R102" s="3">
-        <v>331000</v>
       </c>
       <c r="S102" s="3">
         <v>331000</v>
       </c>
       <c r="T102" s="3">
+        <v>331000</v>
+      </c>
+      <c r="U102" s="3">
         <v>126000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-300000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-120000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1014000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3379000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2458000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>620000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>457000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3115000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>354000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2498000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>927000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3534000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>707000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-709000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-609000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1245000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>780000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1470000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1083000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>875000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-645000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1070000</v>
       </c>
     </row>
